--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484667_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484667_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.8378</v>
+        <v>9.901300000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>8.3032</v>
+        <v>8.3171</v>
       </c>
       <c r="F2" t="n">
-        <v>1.5346</v>
+        <v>1.5841</v>
       </c>
       <c r="G2" t="n">
         <v>7.649</v>
@@ -610,13 +610,13 @@
         <v>1.8326</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.7355</v>
+        <v>-0.672</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.5151</v>
+        <v>-0.5011</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.2204</v>
+        <v>-0.1709</v>
       </c>
       <c r="V2" t="n">
         <v>2.1912</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.901</v>
+        <v>7.5196</v>
       </c>
       <c r="E3" t="n">
-        <v>6.1942</v>
+        <v>6.6889</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7067</v>
+        <v>0.8306</v>
       </c>
       <c r="G3" t="n">
         <v>5.4905</v>
@@ -688,13 +688,13 @@
         <v>1.6493</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.2176</v>
+        <v>-0.599</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.101</v>
+        <v>-0.6063</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1165</v>
+        <v>0.0073</v>
       </c>
       <c r="V3" t="n">
         <v>3.1778</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.1528</v>
+        <v>2.9337</v>
       </c>
       <c r="E4" t="n">
-        <v>3.4482</v>
+        <v>2.9814</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.2954</v>
+        <v>-0.0476</v>
       </c>
       <c r="G4" t="n">
         <v>1.1243</v>
@@ -766,13 +766,13 @@
         <v>1.8326</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.1652</v>
+        <v>-0.3842</v>
       </c>
       <c r="T4" t="n">
-        <v>0.7496</v>
+        <v>0.2828</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.9147999999999999</v>
+        <v>-0.6671</v>
       </c>
       <c r="V4" t="n">
         <v>1.2774</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.3717</v>
+        <v>1.7429</v>
       </c>
       <c r="E5" t="n">
-        <v>2.8115</v>
+        <v>3.0589</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.4398</v>
+        <v>-1.316</v>
       </c>
       <c r="G5" t="n">
         <v>1.6006</v>
@@ -844,13 +844,13 @@
         <v>0.5498</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.7786999999999999</v>
+        <v>-0.4074</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4223</v>
+        <v>-0.175</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3563</v>
+        <v>-0.2325</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2057</v>
+        <v>1.4778</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8421</v>
+        <v>1.0895</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3635</v>
+        <v>0.3883</v>
       </c>
       <c r="G6" t="n">
         <v>1.8325</v>
@@ -922,13 +922,13 @@
         <v>1.4661</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.4594</v>
+        <v>-0.1872</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.7157</v>
+        <v>-0.4683</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2563</v>
+        <v>0.2811</v>
       </c>
       <c r="V6" t="n">
         <v>-1.267</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6921</v>
+        <v>0.2194</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0446</v>
+        <v>-0.3191</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7368</v>
+        <v>0.5386</v>
       </c>
       <c r="G7" t="n">
         <v>-0.5513</v>
@@ -1000,13 +1000,13 @@
         <v>2.0158</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.4059</v>
+        <v>-0.8786</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1666</v>
+        <v>-0.4412</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2392</v>
+        <v>-0.4374</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S. DOMINGUEZ ALEIXANDRE</t>
+          <t>J. ARNAIZ VEGA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.376</v>
+        <v>0.1112</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.1776</v>
+        <v>-0.3148</v>
       </c>
       <c r="F8" t="n">
-        <v>1.5536</v>
+        <v>0.426</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0603</v>
+        <v>0.8367</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.6161</v>
+        <v>-1.0389</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6763</v>
+        <v>1.8756</v>
       </c>
       <c r="J8" t="n">
-        <v>0.3443</v>
+        <v>1.9986</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0525</v>
+        <v>1.2446</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2917</v>
+        <v>0.7539</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.284</v>
+        <v>-1.1618</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.6686</v>
+        <v>-2.2836</v>
       </c>
       <c r="O8" t="n">
-        <v>0.3846</v>
+        <v>1.1217</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.5498</v>
+        <v>-1.2828</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.8326</v>
+        <v>-3.6651</v>
       </c>
       <c r="R8" t="n">
-        <v>1.2828</v>
+        <v>2.3823</v>
       </c>
       <c r="S8" t="n">
-        <v>0.8863</v>
+        <v>-1.0524</v>
       </c>
       <c r="T8" t="n">
-        <v>0.3107</v>
+        <v>-0.2579</v>
       </c>
       <c r="U8" t="n">
-        <v>0.5756</v>
+        <v>-0.7945</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.0208</v>
+        <v>1.6097</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.6097</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.0208</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. ARNAIZ VEGA</t>
+          <t>S. DOMINGUEZ ALEIXANDRE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.3339</v>
+        <v>0.0128</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.8095</v>
+        <v>-1.2187</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4755</v>
+        <v>1.2315</v>
       </c>
       <c r="G9" t="n">
-        <v>0.8367</v>
+        <v>0.0603</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.0389</v>
+        <v>-0.6161</v>
       </c>
       <c r="I9" t="n">
-        <v>1.8756</v>
+        <v>0.6763</v>
       </c>
       <c r="J9" t="n">
-        <v>1.9986</v>
+        <v>0.3443</v>
       </c>
       <c r="K9" t="n">
-        <v>1.2446</v>
+        <v>0.0525</v>
       </c>
       <c r="L9" t="n">
-        <v>0.7539</v>
+        <v>0.2917</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.1618</v>
+        <v>-0.284</v>
       </c>
       <c r="N9" t="n">
-        <v>-2.2836</v>
+        <v>-0.6686</v>
       </c>
       <c r="O9" t="n">
-        <v>1.1217</v>
+        <v>0.3846</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.2828</v>
+        <v>-0.5498</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.6651</v>
+        <v>-1.8326</v>
       </c>
       <c r="R9" t="n">
-        <v>2.3823</v>
+        <v>1.2828</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.4976</v>
+        <v>0.5232</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.7526</v>
+        <v>0.2696</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.745</v>
+        <v>0.2536</v>
       </c>
       <c r="V9" t="n">
-        <v>1.6097</v>
+        <v>-0.0208</v>
       </c>
       <c r="W9" t="n">
-        <v>1.6097</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0.0208</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.5256999999999999</v>
+        <v>-0.7839</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.3386</v>
+        <v>-0.572</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.1871</v>
+        <v>-0.2119</v>
       </c>
       <c r="G10" t="n">
         <v>0.205</v>
@@ -1234,13 +1234,13 @@
         <v>1.6493</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.7857</v>
+        <v>-1.0439</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0355</v>
+        <v>-0.198</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.8212</v>
+        <v>-0.846</v>
       </c>
       <c r="V10" t="n">
         <v>-0.3115</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.8304</v>
+        <v>-0.8085</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.827</v>
+        <v>-0.7308</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.0034</v>
+        <v>-0.07770000000000001</v>
       </c>
       <c r="G11" t="n">
         <v>2.5926</v>
@@ -1312,13 +1312,13 @@
         <v>0.9163</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.4334</v>
+        <v>-0.4116</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4955</v>
+        <v>-0.3993</v>
       </c>
       <c r="U11" t="n">
-        <v>0.062</v>
+        <v>-0.0123</v>
       </c>
       <c r="V11" t="n">
         <v>-1.89</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.5706</v>
+        <v>-6.2241</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.7464</v>
+        <v>-5.499</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.8242</v>
+        <v>-0.7251</v>
       </c>
       <c r="G12" t="n">
         <v>-1.6606</v>
@@ -1390,13 +1390,13 @@
         <v>0.9163</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.9045</v>
+        <v>-0.5581</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1471</v>
+        <v>0.1003</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.7575</v>
+        <v>-0.6584</v>
       </c>
       <c r="V12" t="n">
         <v>-1.2566</v>
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>15.2765</v>
+        <v>16.1022</v>
       </c>
       <c r="E13" t="n">
-        <v>12.6555</v>
+        <v>13.4814</v>
       </c>
       <c r="F13" t="n">
         <v>2.6208</v>
@@ -1468,13 +1468,13 @@
         <v>16.4932</v>
       </c>
       <c r="S13" t="n">
-        <v>-6.497199999999999</v>
+        <v>-5.671200000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>-3.2201</v>
+        <v>-2.3944</v>
       </c>
       <c r="U13" t="n">
-        <v>-3.277</v>
+        <v>-3.2771</v>
       </c>
       <c r="V13" t="n">
         <v>3.510200000000001</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.9163</v>
+        <v>2.2524</v>
       </c>
       <c r="E14" t="n">
-        <v>4.2777</v>
+        <v>2.9315</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.3614</v>
+        <v>-0.6792</v>
       </c>
       <c r="G14" t="n">
         <v>1.3289</v>
@@ -1546,13 +1546,13 @@
         <v>1.6493</v>
       </c>
       <c r="S14" t="n">
-        <v>3.4041</v>
+        <v>1.7402</v>
       </c>
       <c r="T14" t="n">
-        <v>2.0491</v>
+        <v>0.7029</v>
       </c>
       <c r="U14" t="n">
-        <v>1.355</v>
+        <v>1.0373</v>
       </c>
       <c r="V14" t="n">
         <v>-0.6335</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>P. ALVAREZ LABRADOR</t>
+          <t>G. GARCÍA BURGOS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.7563</v>
+        <v>0.9752999999999999</v>
       </c>
       <c r="E15" t="n">
-        <v>3.3546</v>
+        <v>0.9752999999999999</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.5984</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>1.3459</v>
+        <v>0.9752999999999999</v>
       </c>
       <c r="H15" t="n">
-        <v>2.4584</v>
+        <v>0.9752999999999999</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.1125</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>2.952</v>
+        <v>0.9752999999999999</v>
       </c>
       <c r="K15" t="n">
-        <v>3.5513</v>
+        <v>0.9752999999999999</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.5994</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.606</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.0929</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.5131</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.0995</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.9321</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.8326</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>2.1434</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>2.3794</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.236</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.6335</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>0.9554</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.5889</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>G. GARCÍA BURGOS</t>
+          <t>P. ALVAREZ LABRADOR</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9752999999999999</v>
+        <v>0.6331</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9752999999999999</v>
+        <v>2.0085</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>-1.3754</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9752999999999999</v>
+        <v>1.3459</v>
       </c>
       <c r="H16" t="n">
-        <v>0.9752999999999999</v>
+        <v>2.4584</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>-1.1125</v>
       </c>
       <c r="J16" t="n">
-        <v>0.9752999999999999</v>
+        <v>2.952</v>
       </c>
       <c r="K16" t="n">
-        <v>0.9752999999999999</v>
+        <v>3.5513</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>-0.5994</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>-1.606</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>-1.0929</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>-0.5131</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>-1.0995</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-2.9321</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.8326</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>1.0202</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>1.0332</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>-0.013</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>-0.6335</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>0.9554</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-1.5889</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>L. ALBEROLA GUILLOT</t>
+          <t>A. VIVES HURTADO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.4113</v>
+        <v>0.1449</v>
       </c>
       <c r="E17" t="n">
-        <v>0.2218</v>
+        <v>3.2802</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.6332</v>
+        <v>-3.1352</v>
       </c>
       <c r="G17" t="n">
-        <v>-3.465</v>
+        <v>0.0295</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.2982</v>
+        <v>0.7476</v>
       </c>
       <c r="I17" t="n">
-        <v>-2.1668</v>
+        <v>-0.718</v>
       </c>
       <c r="J17" t="n">
-        <v>0.2934</v>
+        <v>3.281</v>
       </c>
       <c r="K17" t="n">
-        <v>1.4982</v>
+        <v>3.2295</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.2048</v>
+        <v>0.0515</v>
       </c>
       <c r="M17" t="n">
-        <v>-3.7584</v>
+        <v>-3.2514</v>
       </c>
       <c r="N17" t="n">
-        <v>-2.7964</v>
+        <v>-2.4819</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.962</v>
+        <v>-0.7695</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.3665</v>
+        <v>1.6493</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.9321</v>
+        <v>-0.1833</v>
       </c>
       <c r="R17" t="n">
-        <v>2.5656</v>
+        <v>1.8326</v>
       </c>
       <c r="S17" t="n">
-        <v>1.2082</v>
+        <v>-0.267</v>
       </c>
       <c r="T17" t="n">
-        <v>0.3266</v>
+        <v>-0.1395</v>
       </c>
       <c r="U17" t="n">
-        <v>0.8816000000000001</v>
+        <v>-0.1275</v>
       </c>
       <c r="V17" t="n">
-        <v>2.212</v>
+        <v>-1.267</v>
       </c>
       <c r="W17" t="n">
-        <v>2.5339</v>
+        <v>0.3219</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.3219</v>
+        <v>-1.5889</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>L. ASSARDO JOVANI</t>
+          <t>L. ALBEROLA GUILLOT</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.0684</v>
+        <v>-0.4754</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.4696</v>
+        <v>0.0295</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.5988</v>
+        <v>-0.5049</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.879</v>
+        <v>-3.465</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.4015</v>
+        <v>-1.2982</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.4775</v>
+        <v>-2.1668</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.0104</v>
+        <v>0.2934</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.4368</v>
+        <v>1.4982</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.5736</v>
+        <v>-1.2048</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.8686</v>
+        <v>-3.7584</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.9647</v>
+        <v>-2.7964</v>
       </c>
       <c r="O18" t="n">
-        <v>0.0961</v>
+        <v>-0.962</v>
       </c>
       <c r="P18" t="n">
-        <v>0.733</v>
+        <v>-0.3665</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.1833</v>
+        <v>-2.9321</v>
       </c>
       <c r="R18" t="n">
-        <v>0.9163</v>
+        <v>2.5656</v>
       </c>
       <c r="S18" t="n">
-        <v>0.711</v>
+        <v>1.1441</v>
       </c>
       <c r="T18" t="n">
-        <v>0.0905</v>
+        <v>0.1343</v>
       </c>
       <c r="U18" t="n">
-        <v>0.6205000000000001</v>
+        <v>1.0098</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.6335</v>
+        <v>2.212</v>
       </c>
       <c r="W18" t="n">
-        <v>0.6335</v>
+        <v>2.5339</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.267</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. VIVES HURTADO</t>
+          <t>G. GARCIA BURGOS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.143</v>
+        <v>-0.5802</v>
       </c>
       <c r="E19" t="n">
-        <v>2.3186</v>
+        <v>-0.5679</v>
       </c>
       <c r="F19" t="n">
-        <v>-3.4616</v>
+        <v>-0.0124</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0295</v>
+        <v>-0.424</v>
       </c>
       <c r="H19" t="n">
-        <v>0.7476</v>
+        <v>0.5603</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.718</v>
+        <v>-0.9843</v>
       </c>
       <c r="J19" t="n">
-        <v>3.281</v>
+        <v>1.663</v>
       </c>
       <c r="K19" t="n">
-        <v>3.2295</v>
+        <v>1.0121</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0515</v>
+        <v>0.6509</v>
       </c>
       <c r="M19" t="n">
-        <v>-3.2514</v>
+        <v>-2.087</v>
       </c>
       <c r="N19" t="n">
-        <v>-2.4819</v>
+        <v>-0.4519</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.7695</v>
+        <v>-1.6351</v>
       </c>
       <c r="P19" t="n">
-        <v>1.6493</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.1833</v>
+        <v>-1.8326</v>
       </c>
       <c r="R19" t="n">
         <v>1.8326</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.5549</v>
+        <v>1.0899</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.101</v>
+        <v>0.5155</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.4539</v>
+        <v>0.5744</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.267</v>
+        <v>-1.2461</v>
       </c>
       <c r="W19" t="n">
-        <v>0.3219</v>
+        <v>-0.9137999999999999</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.5889</v>
+        <v>-0.3324</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>G. GARCIA BURGOS</t>
+          <t>P. LARIO ECHEVARRIAS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.3713</v>
+        <v>-1.0506</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.4332</v>
+        <v>-0.7029</v>
       </c>
       <c r="F20" t="n">
-        <v>0.062</v>
+        <v>-0.3477</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.424</v>
+        <v>-1.0089</v>
       </c>
       <c r="H20" t="n">
-        <v>0.5603</v>
+        <v>-0.2075</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.9843</v>
+        <v>-0.8014</v>
       </c>
       <c r="J20" t="n">
-        <v>1.663</v>
+        <v>-0.1983</v>
       </c>
       <c r="K20" t="n">
-        <v>1.0121</v>
+        <v>0.4427</v>
       </c>
       <c r="L20" t="n">
-        <v>0.6509</v>
+        <v>-0.641</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.087</v>
+        <v>-0.8106</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.4519</v>
+        <v>-0.6502</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.6351</v>
+        <v>-0.1603</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>-0.3665</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.8326</v>
+        <v>-0.9163</v>
       </c>
       <c r="R20" t="n">
-        <v>1.8326</v>
+        <v>0.5498</v>
       </c>
       <c r="S20" t="n">
-        <v>0.2989</v>
+        <v>0.3249</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3499</v>
+        <v>0.4118</v>
       </c>
       <c r="U20" t="n">
-        <v>0.6488</v>
+        <v>-0.08690000000000001</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.2461</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.9137999999999999</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.3324</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.4487</v>
+        <v>-1.1106</v>
       </c>
       <c r="E21" t="n">
-        <v>0.1362</v>
+        <v>0.4247</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.5849</v>
+        <v>-1.5353</v>
       </c>
       <c r="G21" t="n">
         <v>-1.9555</v>
@@ -2092,13 +2092,13 @@
         <v>1.0995</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2603</v>
+        <v>0.07770000000000001</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.7157</v>
+        <v>-0.4272</v>
       </c>
       <c r="U21" t="n">
-        <v>0.4553</v>
+        <v>0.5049</v>
       </c>
       <c r="V21" t="n">
         <v>-0.3324</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>P. LARIO ECHEVARRIAS</t>
+          <t>L. ASSARDO JOVANI</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.6523</v>
+        <v>-1.1705</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.2798</v>
+        <v>-0.3735</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.3725</v>
+        <v>-0.797</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.0089</v>
+        <v>-1.879</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.2075</v>
+        <v>-1.4015</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.8014</v>
+        <v>-0.4775</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.1983</v>
+        <v>-1.0104</v>
       </c>
       <c r="K22" t="n">
-        <v>0.4427</v>
+        <v>-0.4368</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.641</v>
+        <v>-0.5736</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.8106</v>
+        <v>-0.8686</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.6502</v>
+        <v>-0.9647</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.1603</v>
+        <v>0.0961</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.3665</v>
+        <v>0.733</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.9163</v>
+        <v>-0.1833</v>
       </c>
       <c r="R22" t="n">
-        <v>0.5498</v>
+        <v>0.9163</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2768</v>
+        <v>0.609</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1652</v>
+        <v>0.1867</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1117</v>
+        <v>0.4223</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>-0.6335</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>0.6335</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-1.267</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>J. ESTARLICH MARTINEZ</t>
+          <t>I. EGIDO MUNOZ</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.1726</v>
+        <v>-2.8265</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.6963</v>
+        <v>-3.1953</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.4763</v>
+        <v>0.3688</v>
       </c>
       <c r="G23" t="n">
-        <v>-3.3037</v>
+        <v>-1.9602</v>
       </c>
       <c r="H23" t="n">
-        <v>0.95</v>
+        <v>-0.9537</v>
       </c>
       <c r="I23" t="n">
-        <v>-4.2537</v>
+        <v>-1.0065</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.9527</v>
+        <v>-1.0687</v>
       </c>
       <c r="K23" t="n">
-        <v>1.5697</v>
+        <v>-0.511</v>
       </c>
       <c r="L23" t="n">
-        <v>-2.5224</v>
+        <v>-0.5577</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.351</v>
+        <v>-0.8915999999999999</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.6198</v>
+        <v>-0.4427</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.7312</v>
+        <v>-0.4489</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.0995</v>
+        <v>-0.9163</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.7489</v>
+        <v>-2.0158</v>
       </c>
       <c r="R23" t="n">
-        <v>1.6493</v>
+        <v>1.0995</v>
       </c>
       <c r="S23" t="n">
-        <v>1.8641</v>
+        <v>0.05</v>
       </c>
       <c r="T23" t="n">
-        <v>1.6833</v>
+        <v>-0.1108</v>
       </c>
       <c r="U23" t="n">
-        <v>0.1808</v>
+        <v>0.1608</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.6335</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>0.3219</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.9554</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>I. EGIDO MUNOZ</t>
+          <t>A. GUTIERREZ MARCO</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.1864</v>
+        <v>-3.5611</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.58</v>
+        <v>-2.1228</v>
       </c>
       <c r="F24" t="n">
-        <v>0.3936</v>
+        <v>-1.4382</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.9602</v>
+        <v>-4.5043</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.9537</v>
+        <v>-3.081</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.0065</v>
+        <v>-1.4233</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.0687</v>
+        <v>-2.329</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.511</v>
+        <v>-1.7714</v>
       </c>
       <c r="L24" t="n">
         <v>-0.5577</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.8915999999999999</v>
+        <v>-2.1753</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.4427</v>
+        <v>-1.3097</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.4489</v>
+        <v>-0.8656</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.9163</v>
+        <v>0.9163</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.0158</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.0995</v>
+        <v>0.9163</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.3099</v>
+        <v>0.027</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.4955</v>
+        <v>-0.1157</v>
       </c>
       <c r="U24" t="n">
-        <v>0.1856</v>
+        <v>0.1427</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>0.3219</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A. GUTIERREZ MARCO</t>
+          <t>M. SHALABI TORRES</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,73 +2359,73 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.4692</v>
+        <v>-3.7816</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.0267</v>
+        <v>-2.6503</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.4426</v>
+        <v>-1.1313</v>
       </c>
       <c r="G25" t="n">
-        <v>-4.5043</v>
+        <v>-4.3587</v>
       </c>
       <c r="H25" t="n">
-        <v>-3.081</v>
+        <v>-0.5059</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.4233</v>
+        <v>-3.8528</v>
       </c>
       <c r="J25" t="n">
-        <v>-2.329</v>
+        <v>-1.1637</v>
       </c>
       <c r="K25" t="n">
-        <v>-1.7714</v>
+        <v>1.3747</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.5577</v>
+        <v>-2.5383</v>
       </c>
       <c r="M25" t="n">
-        <v>-2.1753</v>
+        <v>-3.195</v>
       </c>
       <c r="N25" t="n">
-        <v>-1.3097</v>
+        <v>-1.8805</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.8656</v>
+        <v>-1.3145</v>
       </c>
       <c r="P25" t="n">
-        <v>0.9163</v>
+        <v>0.5498</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>-0.9163</v>
       </c>
       <c r="R25" t="n">
-        <v>0.9163</v>
+        <v>1.4661</v>
       </c>
       <c r="S25" t="n">
-        <v>0.1188</v>
+        <v>0.3701</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.0196</v>
+        <v>0.3643</v>
       </c>
       <c r="U25" t="n">
-        <v>0.1384</v>
+        <v>0.0058</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>-0.3428</v>
       </c>
       <c r="W25" t="n">
-        <v>0.3219</v>
+        <v>-0.9346</v>
       </c>
       <c r="X25" t="n">
-        <v>-0.3219</v>
+        <v>0.5918</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>M. SHALABI TORRES</t>
+          <t>J. ESTARLICH MARTINEZ</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-5.0011</v>
+        <v>-4.0846</v>
       </c>
       <c r="E26" t="n">
-        <v>-3.4195</v>
+        <v>-2.6579</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.5816</v>
+        <v>-1.4267</v>
       </c>
       <c r="G26" t="n">
-        <v>-4.3587</v>
+        <v>-3.3037</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.5059</v>
+        <v>0.95</v>
       </c>
       <c r="I26" t="n">
-        <v>-3.8528</v>
+        <v>-4.2537</v>
       </c>
       <c r="J26" t="n">
-        <v>-1.1637</v>
+        <v>-0.9527</v>
       </c>
       <c r="K26" t="n">
-        <v>1.3747</v>
+        <v>1.5697</v>
       </c>
       <c r="L26" t="n">
-        <v>-2.5383</v>
+        <v>-2.5224</v>
       </c>
       <c r="M26" t="n">
-        <v>-3.195</v>
+        <v>-2.351</v>
       </c>
       <c r="N26" t="n">
-        <v>-1.8805</v>
+        <v>-0.6198</v>
       </c>
       <c r="O26" t="n">
-        <v>-1.3145</v>
+        <v>-1.7312</v>
       </c>
       <c r="P26" t="n">
-        <v>0.5498</v>
+        <v>-1.0995</v>
       </c>
       <c r="Q26" t="n">
-        <v>-0.9163</v>
+        <v>-2.7489</v>
       </c>
       <c r="R26" t="n">
-        <v>1.4661</v>
+        <v>1.6493</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.8494</v>
+        <v>0.9520999999999999</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.405</v>
+        <v>0.7217</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.4444</v>
+        <v>0.2304</v>
       </c>
       <c r="V26" t="n">
-        <v>-0.3428</v>
+        <v>-0.6335</v>
       </c>
       <c r="W26" t="n">
-        <v>-0.9346</v>
+        <v>0.3219</v>
       </c>
       <c r="X26" t="n">
-        <v>0.5918</v>
+        <v>-0.9554</v>
       </c>
     </row>
     <row r="27">
@@ -2515,19 +2515,19 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-15.2764</v>
+        <v>-14.6354</v>
       </c>
       <c r="E27" t="n">
-        <v>-2.620900000000001</v>
+        <v>-2.620899999999998</v>
       </c>
       <c r="F27" t="n">
-        <v>-12.6557</v>
+        <v>-12.0145</v>
       </c>
       <c r="G27" t="n">
         <v>-19.1797</v>
       </c>
       <c r="H27" t="n">
-        <v>0.5347000000000008</v>
+        <v>0.5346999999999993</v>
       </c>
       <c r="I27" t="n">
         <v>-19.7143</v>
@@ -2539,7 +2539,7 @@
         <v>15.8445</v>
       </c>
       <c r="L27" t="n">
-        <v>-9.1335</v>
+        <v>-9.133500000000002</v>
       </c>
       <c r="M27" t="n">
         <v>-25.8907</v>
@@ -2551,7 +2551,7 @@
         <v>-10.5806</v>
       </c>
       <c r="P27" t="n">
-        <v>0.9162999999999998</v>
+        <v>0.9162999999999997</v>
       </c>
       <c r="Q27" t="n">
         <v>-16.4933</v>
@@ -2560,19 +2560,19 @@
         <v>17.4095</v>
       </c>
       <c r="S27" t="n">
-        <v>6.497200000000001</v>
+        <v>7.138199999999999</v>
       </c>
       <c r="T27" t="n">
-        <v>3.277</v>
+        <v>3.277200000000001</v>
       </c>
       <c r="U27" t="n">
-        <v>3.22</v>
+        <v>3.861</v>
       </c>
       <c r="V27" t="n">
         <v>-3.5103</v>
       </c>
       <c r="W27" t="n">
-        <v>3.884000000000001</v>
+        <v>3.884</v>
       </c>
       <c r="X27" t="n">
         <v>-7.3943</v>
